--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-Next-80B-A3B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-Next-80B-A3B-Instruct/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>132</v>
+        <v>46</v>
       </c>
       <c r="D2">
-        <v>195</v>
+        <v>380</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="D3">
-        <v>299</v>
+        <v>343</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-Next-80B-A3B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-Next-80B-A3B-Instruct/aae/total_votes_file.xlsx
@@ -430,10 +430,10 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D2">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -450,7 +450,7 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D3">
         <v>343</v>
@@ -459,7 +459,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>426</v>
